--- a/data/trans_camb/P12_1_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 0,63</t>
+          <t>-6,25; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,21</t>
+          <t>-5,37; 2,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,91</t>
+          <t>-4,08; 3,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,4</t>
+          <t>2,84; 11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,3</t>
+          <t>-5,0; 3,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,16</t>
+          <t>-3,3; 3,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,02</t>
+          <t>-0,8; 5,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,77</t>
+          <t>-3,84; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,96</t>
+          <t>-2,33; 2,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 4,62</t>
+          <t>-36,25; 5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 23,68</t>
+          <t>-31,55; 15,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 29,14</t>
+          <t>-22,8; 27,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 68,93</t>
+          <t>13,04; 70,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 19,74</t>
+          <t>-24,38; 18,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 25,73</t>
+          <t>-15,62; 24,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 31,84</t>
+          <t>-4,42; 31,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 11,27</t>
+          <t>-20,33; 10,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 19,23</t>
+          <t>-12,47; 17,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 1,45</t>
+          <t>-5,27; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -4,06</t>
+          <t>-10,69; -4,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -5,99</t>
+          <t>-15,03; -6,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 3,66</t>
+          <t>-4,12; 3,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -5,14</t>
+          <t>-12,06; -4,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -2,59</t>
+          <t>-9,34; -2,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,57</t>
+          <t>-3,54; 1,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -5,5</t>
+          <t>-10,38; -5,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -5,77</t>
+          <t>-13,2; -5,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 9,18</t>
+          <t>-27,22; 9,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,15; -25,88</t>
+          <t>-53,8; -25,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,74; -36,27</t>
+          <t>-77,3; -37,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 16,94</t>
+          <t>-16,04; 14,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,82; -22,25</t>
+          <t>-46,51; -21,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,52; -11,56</t>
+          <t>-36,63; -11,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 7,87</t>
+          <t>-15,71; 9,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,65; -28,3</t>
+          <t>-46,65; -28,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,25; -29,05</t>
+          <t>-61,0; -28,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 1,87</t>
+          <t>-6,13; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; -3,05</t>
+          <t>-10,17; -2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,85</t>
+          <t>-6,54; 2,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,81</t>
+          <t>-2,0; 6,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -2,06</t>
+          <t>-10,63; -2,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 43,04</t>
+          <t>-6,89; 44,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,18</t>
+          <t>-2,79; 3,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -3,35</t>
+          <t>-9,67; -3,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 30,36</t>
+          <t>-4,84; 29,85</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 12,44</t>
+          <t>-31,62; 11,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,45; -19,68</t>
+          <t>-52,45; -16,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 12,81</t>
+          <t>-34,49; 13,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 32,33</t>
+          <t>-8,18; 32,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,06; -9,92</t>
+          <t>-42,33; -11,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 219,97</t>
+          <t>-29,06; 200,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 17,13</t>
+          <t>-13,08; 18,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,6; -18,27</t>
+          <t>-43,98; -19,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 161,66</t>
+          <t>-23,31; 150,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,11</t>
+          <t>-1,95; 4,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; -1,33</t>
+          <t>-7,76; -1,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,07</t>
+          <t>-5,3; 0,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,57</t>
+          <t>1,43; 9,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -2,43</t>
+          <t>-9,28; -2,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1,1</t>
+          <t>-7,63; 1,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,31</t>
+          <t>0,92; 5,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -2,98</t>
+          <t>-8,09; -2,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,67</t>
+          <t>-5,43; 0,16</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 33,31</t>
+          <t>-10,87; 31,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -7,75</t>
+          <t>-41,74; -8,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 8,58</t>
+          <t>-29,05; 6,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 44,56</t>
+          <t>6,05; 43,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,83; -11,23</t>
+          <t>-37,8; -10,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,94</t>
+          <t>-30,4; 5,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 32,77</t>
+          <t>4,34; 31,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,11; -15,77</t>
+          <t>-37,33; -15,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 3,41</t>
+          <t>-24,68; 0,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,61</t>
+          <t>-3,03; 0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -3,5</t>
+          <t>-7,05; -3,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,44</t>
+          <t>-7,39; -2,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,88</t>
+          <t>1,54; 5,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -3,86</t>
+          <t>-7,58; -3,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 15,33</t>
+          <t>-4,1; 16,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,63</t>
+          <t>-0,13; 2,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -4,24</t>
+          <t>-6,79; -4,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,37</t>
+          <t>-4,6; 7,13</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 3,99</t>
+          <t>-17,19; 4,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -21,84</t>
+          <t>-39,67; -22,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,48; -15,11</t>
+          <t>-42,83; -15,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,97; 27,48</t>
+          <t>6,57; 25,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -18,08</t>
+          <t>-32,31; -17,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 68,27</t>
+          <t>-18,05; 74,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,74</t>
+          <t>-0,68; 14,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-33,16; -22,08</t>
+          <t>-33,21; -21,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 32,19</t>
+          <t>-23,09; 37,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_1_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 0,75</t>
+          <t>-6,28; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,12</t>
+          <t>-5,21; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,64</t>
+          <t>-4,1; 3,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,87</t>
+          <t>2,9; 11,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,09</t>
+          <t>-4,64; 3,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,91</t>
+          <t>-4,09; 3,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,07</t>
+          <t>-1,18; 4,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,73</t>
+          <t>-3,86; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,65</t>
+          <t>-2,83; 2,36</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,48%</t>
+          <t>-2,93%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>-0,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>-0,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 5,85</t>
+          <t>-36,38; 7,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 15,32</t>
+          <t>-30,21; 17,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 27,54</t>
+          <t>-23,75; 27,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,04; 70,49</t>
+          <t>14,42; 71,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 18,21</t>
+          <t>-23,11; 21,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 24,2</t>
+          <t>-19,64; 22,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 31,96</t>
+          <t>-5,89; 32,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 10,84</t>
+          <t>-21,39; 10,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 17,29</t>
+          <t>-14,94; 15,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,59</t>
+          <t>-7,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,02</t>
+          <t>-5,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,33</t>
+          <t>-6,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 1,44</t>
+          <t>-4,73; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; -4,24</t>
+          <t>-10,49; -3,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -6,02</t>
+          <t>-10,56; -4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,21</t>
+          <t>-4,14; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,94</t>
+          <t>-12,11; -5,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,34; -2,33</t>
+          <t>-9,13; -2,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,88</t>
+          <t>-3,82; 1,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; -5,45</t>
+          <t>-10,38; -5,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -5,58</t>
+          <t>-9,08; -4,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-53,73%</t>
+          <t>-41,1%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,29%</t>
+          <t>-24,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-40,01%</t>
+          <t>-31,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 9,14</t>
+          <t>-24,93; 11,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,8; -25,65</t>
+          <t>-54,13; -22,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,3; -37,53</t>
+          <t>-53,58; -25,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 14,81</t>
+          <t>-15,97; 17,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,51; -21,46</t>
+          <t>-46,71; -22,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,63; -11,42</t>
+          <t>-35,46; -11,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 9,74</t>
+          <t>-17,1; 8,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -28,4</t>
+          <t>-47,21; -28,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,0; -28,33</t>
+          <t>-40,34; -22,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-3,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,68</t>
+          <t>-4,34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>-3,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 1,78</t>
+          <t>-6,5; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -2,74</t>
+          <t>-10,67; -3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 2,03</t>
+          <t>-6,92; 1,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,92</t>
+          <t>-2,06; 6,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -2,35</t>
+          <t>-11,17; -2,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 44,24</t>
+          <t>-8,4; -0,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,43</t>
+          <t>-2,75; 3,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -3,67</t>
+          <t>-9,18; -3,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 29,85</t>
+          <t>-6,81; -0,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,17%</t>
+          <t>-18,02%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>-18,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>-18,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 11,65</t>
+          <t>-33,24; 15,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -16,05</t>
+          <t>-55,06; -19,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 13,24</t>
+          <t>-36,52; 7,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 32,48</t>
+          <t>-8,2; 34,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,33; -11,45</t>
+          <t>-43,87; -12,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 200,52</t>
+          <t>-33,05; -2,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 18,63</t>
+          <t>-12,82; 17,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,98; -19,72</t>
+          <t>-43,11; -20,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 150,74</t>
+          <t>-31,07; -4,72</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-1,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,78</t>
+          <t>-2,49; 4,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -1,38</t>
+          <t>-7,92; -1,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,98</t>
+          <t>-5,35; 1,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,24</t>
+          <t>1,48; 9,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -2,23</t>
+          <t>-9,61; -2,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,12</t>
+          <t>-4,52; 2,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,94</t>
+          <t>0,63; 5,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -2,92</t>
+          <t>-7,9; -3,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,16</t>
+          <t>-4,0; 0,64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-13,15%</t>
+          <t>-13,16%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,61%</t>
+          <t>-4,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,13%</t>
+          <t>-7,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 31,13</t>
+          <t>-13,5; 30,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -8,93</t>
+          <t>-42,68; -11,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 6,28</t>
+          <t>-28,88; 7,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 43,97</t>
+          <t>5,96; 42,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -10,42</t>
+          <t>-38,44; -10,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 5,08</t>
+          <t>-17,82; 10,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 31,44</t>
+          <t>2,96; 31,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,33; -15,35</t>
+          <t>-37,0; -16,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 0,97</t>
+          <t>-18,52; 3,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,35</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>-2,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-3,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,74</t>
+          <t>-2,94; 0,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -3,58</t>
+          <t>-6,95; -3,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -2,42</t>
+          <t>-5,22; -1,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,6</t>
+          <t>1,65; 5,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -3,87</t>
+          <t>-7,73; -3,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 16,55</t>
+          <t>-4,91; -1,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,71</t>
+          <t>-0,11; 2,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -4,21</t>
+          <t>-6,75; -4,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 7,13</t>
+          <t>-4,53; -1,92</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-25,71%</t>
+          <t>-21,04%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>-12,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,75%</t>
+          <t>-16,16%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 4,68</t>
+          <t>-16,69; 4,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -22,97</t>
+          <t>-38,7; -21,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,83; -15,18</t>
+          <t>-29,44; -10,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,57; 25,85</t>
+          <t>7,11; 27,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,31; -17,12</t>
+          <t>-33,12; -18,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 74,73</t>
+          <t>-20,72; -4,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 14,2</t>
+          <t>-0,55; 14,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-33,21; -21,98</t>
+          <t>-33,27; -22,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 37,13</t>
+          <t>-22,08; -10,02</t>
         </is>
       </c>
     </row>
